--- a/codebook.xlsx
+++ b/codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agzhang/Desktop/Third year/PSTAT 131/project/project data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/agzhang/Desktop/Career/projects/loan-prediction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428D4263-42BB-124C-B881-E9C3FC838A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A1C890-4E4C-8B45-A88C-24AFD5E7C3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13340" yWindow="680" windowWidth="14020" windowHeight="15820" xr2:uid="{762A26FF-0690-AD44-99A5-46BC924388E7}"/>
+    <workbookView xWindow="13340" yWindow="560" windowWidth="14020" windowHeight="15820" xr2:uid="{762A26FF-0690-AD44-99A5-46BC924388E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">Variable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Description</t>
   </si>
@@ -65,69 +59,27 @@
     <t>ApplicantIncome</t>
   </si>
   <si>
-    <t>Applicant income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coapplicant income </t>
-  </si>
-  <si>
-    <t>Self-employed</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Property area</t>
-  </si>
-  <si>
-    <t>Loan amount in thousands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Term of loan in months </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique loan ID </t>
-  </si>
-  <si>
     <t>character</t>
   </si>
   <si>
-    <t>Values</t>
-  </si>
-  <si>
     <t>integer</t>
   </si>
   <si>
-    <t>1/0 (Yes/No)</t>
-  </si>
-  <si>
-    <t>Credit history meets guidelines</t>
-  </si>
-  <si>
     <t>Male / Female</t>
   </si>
   <si>
-    <t xml:space="preserve">Gender </t>
-  </si>
-  <si>
     <t>Yes / No</t>
   </si>
   <si>
-    <t>0,1,2,3+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dependents </t>
-  </si>
-  <si>
     <t>Graduate / Not Graduate</t>
   </si>
   <si>
     <t>Urban / Semiurban / Rural</t>
   </si>
   <si>
-    <t>Loan approved</t>
-  </si>
-  <si>
     <t>CoapplicantIncome</t>
   </si>
   <si>
@@ -144,22 +96,80 @@
   </si>
   <si>
     <t>Loan_Status</t>
+  </si>
+  <si>
+    <t>Number of dependents</t>
+  </si>
+  <si>
+    <t>Applicant's education level</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Values / Units</t>
+  </si>
+  <si>
+    <t>Unique loan ID</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Gender of the applicant</t>
+  </si>
+  <si>
+    <t>Marital status</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3+</t>
+  </si>
+  <si>
+    <t>Whether the applicant is self-employed</t>
+  </si>
+  <si>
+    <t>Applicant's monthly income</t>
+  </si>
+  <si>
+    <t>Dollar amount (USD)</t>
+  </si>
+  <si>
+    <t>Coapplicant's monthly income</t>
+  </si>
+  <si>
+    <t>Loan amount requested</t>
+  </si>
+  <si>
+    <t>Thousands of dollars</t>
+  </si>
+  <si>
+    <t>Term of loan</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Whether credit history meets bank's requirements</t>
+  </si>
+  <si>
+    <t>1 (Meets) / 0 (Does not meet)</t>
+  </si>
+  <si>
+    <t>Applicant's area of residence</t>
+  </si>
+  <si>
+    <t>Loan approval status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -198,11 +208,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,190 +529,205 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>18</v>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4">
